--- a/docs/research/provinces/SportsHub-Alberta.xlsx
+++ b/docs/research/provinces/SportsHub-Alberta.xlsx
@@ -11,12 +11,14 @@
     <sheet name="Leagues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Club-League Map" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Contacts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Club Sizes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$204</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$240</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Club Sizes'!$A$1:$C$131</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -562,13 +564,11 @@
           <t>Box 740, T0M 1J0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>rustlers.girls.basketball@gmail.com</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Chris King, Executive Director</t>
@@ -579,13 +579,11 @@
           <t>Girls youth basketball for Acme/Linden (Kneehill County) area</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>community club (girls)</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>primary</t>
@@ -628,7 +626,6 @@
           <t>P.O. Box 10176, Airdrie, AB T4A 0H5</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>info@airdriebasketball.ca</t>
@@ -674,7 +671,6 @@
           <t>https://airdriebasketball.ca/executive</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -697,7 +693,6 @@
           <t>Airdrie</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>403-554-9479</t>
@@ -785,8 +780,6 @@
           <t>403-999-8074</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Jamie Newman, Director of Basketball Operations</t>
@@ -797,13 +790,11 @@
           <t>Boys &amp; girls travel teams U13-U17 for Airdrie, Cochrane, Three Hills, Didsbury area; plays major Alberta club tournaments; exposure to CIS/ACAC scouts</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>community club (competitive travel)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>verified</t>
@@ -841,7 +832,6 @@
           <t>Barrhead</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>587-336-7879</t>
@@ -852,7 +842,6 @@
           <t>brettgitzel@gmail.com</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Brett Gitzel — club contact (AYBC directory)</t>
@@ -873,7 +862,6 @@
           <t>community club</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>primary</t>
@@ -993,7 +981,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>403-465-0743</t>
@@ -1029,7 +1016,6 @@
           <t>private academy / elite club</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>verified</t>
@@ -1067,7 +1053,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>403-803-4403</t>
@@ -1118,7 +1103,6 @@
           <t>http://albertashootingstars.com</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1146,14 +1130,11 @@
           <t>14 Royal Vista Link NW, Calgary</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>https://alonzolutions.ca/</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Elite-level coaching/training for all skill levels; team-concept elite 3-month programs; camps; trains in Okotoks and Calgary</t>
@@ -1211,8 +1192,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>president@bowriverbasketball.com</t>
@@ -1290,7 +1269,6 @@
           <t>292212 Wagon Wheel Blvd, Bay 12, Rocky View County, T4A 0E2</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>info@brodierec.com</t>
@@ -1321,7 +1299,6 @@
           <t>private rec league operator</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>reported</t>
@@ -1359,7 +1336,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>403-400-6971</t>
@@ -1370,7 +1346,6 @@
           <t>ryan.l.scruggs@gmail.com</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Ryan Scruggs — contact (AYBC record)</t>
@@ -1391,7 +1366,6 @@
           <t>community club (possible school-affiliated club team — affiliation unconfirmed)</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -1429,8 +1403,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>info@ctawest.com</t>
@@ -1451,7 +1423,6 @@
           <t>Post-graduate prep basketball; rosters 2020/21-2025/26; 90% post-secondary placement claim; athletes housed at Best Western Executive Residency</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>private academy (post-grad prep, with dorms)</t>
@@ -1472,7 +1443,6 @@
           <t>https://www.ctawest.com/staff-bios</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1577,7 +1547,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>(825) 438-3316</t>
@@ -1598,14 +1567,11 @@
           <t>Martin Kratky — Director / Head Coach</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>community club (details unpublished)</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -1643,8 +1609,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>info@calgarybasketball.ca</t>
@@ -1717,8 +1681,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>calgarychinooksbasketball@gmail.com</t>
@@ -1729,7 +1691,6 @@
           <t>https://www.calgarychinooksbasketball.com</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>North Calgary; U9-U17 boys/girls/coed; fundamentals, competitive local and travel teams; fall tryouts, summer camps</t>
@@ -1787,11 +1748,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>U15 boys club team evidenced</t>
@@ -1807,7 +1763,6 @@
           <t>private club</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>reported</t>
@@ -1818,7 +1773,6 @@
           <t>https://www.cmba.ab.ca/team/7743/302/22786/173471</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1846,7 +1800,6 @@
           <t>Box 401, 918 - 16 Avenue NW, Calgary, AB T2M 0K3</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>grizzlies@calgarygrizzlies.ab.ca</t>
@@ -1867,13 +1820,11 @@
           <t>Weekly recreational wheelchair basketball at Mount Royal University; open to all ages/abilities, disabled or able-bodied</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>community nonprofit (adaptive/wheelchair, all ages incl. youth)</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>verified</t>
@@ -1911,7 +1862,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>(403) 702-5880</t>
@@ -1962,7 +1912,6 @@
           <t>https://www.calgaryimpactbasketball.com</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2005,7 +1954,6 @@
           <t>https://www.cmba.ab.ca/</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>Operates Fall/Winter League (zone teams only), Spring League (zone + independent club teams), Diamond Prep League; 10-11 zone member associations</t>
@@ -2063,8 +2011,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>calgarynwbasketball@gmail.com</t>
@@ -2137,7 +2083,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>403-808-2986</t>
@@ -2215,7 +2160,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>587-719-0119</t>
@@ -2231,13 +2175,11 @@
           <t>https://csbasketball.academy</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Founded Jan 2025; youth development ages 5-17; competitive teams U11-U18; camps/clinics; invitation-only high performance academy</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>private academy</t>
@@ -2258,7 +2200,6 @@
           <t>https://csbasketball.academy</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2286,7 +2227,6 @@
           <t>PO Box 31023, RPO Bridgeland, Calgary, AB T2E 9A3</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>registrar@thunderbasketball.ca</t>
@@ -2297,9 +2237,6 @@
           <t>http://thunderbasketball.ca/</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>community club</t>
@@ -2347,7 +2284,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>430-874-3120</t>
@@ -2430,7 +2366,6 @@
           <t>PO Box 96043, 4000 873 85 St SW, Calgary, AB T3H 0J0</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>Calwest.president@gmail.com</t>
@@ -2503,7 +2438,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>403-540-1693</t>
@@ -2514,7 +2448,6 @@
           <t>vanhooren1@shaw.ca</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Kara Vanhooren — contact (AYBC record)</t>
@@ -2535,7 +2468,6 @@
           <t>community club (parent/coach-run)</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>primary</t>
@@ -2546,7 +2478,6 @@
           <t>https://www.aybc.ca/2020-club-members-1/develop</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2569,7 +2500,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>403-614-0918</t>
@@ -2580,7 +2510,6 @@
           <t>dunksbball@gmail.com</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Dixon Dunkle — contact (AYBC record)</t>
@@ -2601,7 +2530,6 @@
           <t>community club</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>primary</t>
@@ -2612,7 +2540,6 @@
           <t>https://www.aybc.ca/2020-club-members-1/dunks-basketball</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2640,7 +2567,6 @@
           <t>5206 - 68th Street NE, Calgary, AB</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>nardinecain@hotmail.com</t>
@@ -2733,7 +2659,6 @@
           <t>http://eastviewbb.ca/</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Non-profit developing basketball skills for kids of all ages</t>
@@ -2955,9 +2880,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>https://www.fcbablizzards.com/</t>
@@ -2983,7 +2905,6 @@
           <t>community club (cultural community organization)</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>verified</t>
@@ -3021,7 +2942,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>587-887-5460</t>
@@ -3057,7 +2977,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>verified</t>
@@ -3095,7 +3014,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>587-888-5038</t>
@@ -3173,7 +3091,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>403-870-3420</t>
@@ -3256,7 +3173,6 @@
           <t>635 Northmount Dr NW, Calgary, AB T2K 3J6</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>admin@iconsbasketball.ca</t>
@@ -3267,15 +3183,11 @@
           <t>https://iconsbasketball.ca/</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>private club</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>reported</t>
@@ -3313,7 +3225,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>403-614-4929</t>
@@ -3324,8 +3235,6 @@
           <t>jejensen@gmail.com</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>U19 boys</t>
@@ -3341,7 +3250,6 @@
           <t>community club (parent/coach-run)</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3379,7 +3287,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>403-921-0411</t>
@@ -3390,7 +3297,6 @@
           <t>loewenlee@gmail.com</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Lee Loewen — contact (AYBC record)</t>
@@ -3411,7 +3317,6 @@
           <t>community club / trainer-run</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3422,7 +3327,6 @@
           <t>https://www.aybc.ca/2020-club-members-1/lee-loewen-basketball</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3445,8 +3349,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>darryl.movefree@gmail.com</t>
@@ -3457,19 +3359,16 @@
           <t>https://www.facebook.com/legendsbasketball.yyc/</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Drop-in skills sessions prepping players for school season</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>community club / skills program</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -3507,7 +3406,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>(403) 903-3650</t>
@@ -3585,7 +3483,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>403-604-4717</t>
@@ -3596,7 +3493,6 @@
           <t>dipahasan@gmail.com</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Dipa Hasan — contact (AYBC record)</t>
@@ -3617,7 +3513,6 @@
           <t>community club (parent/coach-run)</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3628,7 +3523,6 @@
           <t>https://www.aybc.ca/2020-club-members-1/misfits</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3651,7 +3545,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>403-604-4717</t>
@@ -3662,7 +3555,6 @@
           <t>dipahasan@gmail.com</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Dipa Hasan — club contact (AYBC directory)</t>
@@ -3683,7 +3575,6 @@
           <t>private club (girls)</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>reported</t>
@@ -3694,7 +3585,6 @@
           <t>https://www.aybc.ca/2020-club-members-1/misfits</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3717,7 +3607,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>(403) 973-6665</t>
@@ -3795,7 +3684,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>403-993-0419</t>
@@ -3806,7 +3694,6 @@
           <t>pushkar.chicago@gmail.com</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Pushkar Rao — contact (AYBC record)</t>
@@ -3827,7 +3714,6 @@
           <t>community club (parent/coach-run)</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3838,7 +3724,6 @@
           <t>https://www.aybc.ca/2020-club-members-1/nw-warriors</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3861,19 +3746,11 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>private club</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>reported</t>
@@ -3911,7 +3788,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>587-226-2080</t>
@@ -3922,7 +3798,6 @@
           <t>piccirillojeff@gmail.com</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Jeff Piccirillo — contact (AYBC record)</t>
@@ -3943,7 +3818,6 @@
           <t>community club (parent/coach-run)</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3954,7 +3828,6 @@
           <t>https://www.aybc.ca/2020-club-members-1/northwest-bulldogs</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3977,7 +3850,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>403-589-6018</t>
@@ -4055,7 +3927,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>403-861-2119</t>
@@ -4066,7 +3937,6 @@
           <t>purehoopsinfo@gmail.com</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Ray Raymond — contact (AYBC record)</t>
@@ -4087,7 +3957,6 @@
           <t>community club</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4098,7 +3967,6 @@
           <t>https://www.aybc.ca/2020-club-members-1/purehoops-basketball-club</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4121,19 +3989,11 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>private club</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>reported</t>
@@ -4191,19 +4051,16 @@
           <t>https://prolificsportsacademy.com/</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>Preparatory boarding-school basketball program founded 2022 for boys grades 10-12 and postgraduates; affiliated with Prolific Sports House facility</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>private academy (prep boarding program, boys gr.10-12 + postgrad)</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4328,14 +4185,11 @@
           <t>#01, 33 St NE, Calgary, AB T2E 7K1</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>https://www.rise-basketball.com/</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>Founded 2015; 5,000+ athletes/yr; training, academy, strength &amp; conditioning, in-house seasonal leagues, drop-ins, camps; ages 5-18 plus adult</t>
@@ -4393,7 +4247,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>403-681-1606</t>
@@ -4444,7 +4297,6 @@
           <t>https://www.redstarbasketball.com</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4467,8 +4319,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>respectbball@gmail.com</t>
@@ -4479,13 +4329,11 @@
           <t>https://www.respectbasketball.ca</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>Ages 6-18 (Rookie/Freshman/Sophomore/Junior/Senior squads U10-U18); no-cut skill-based placement; competitive travel teams + development; fall/winter/spring</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
           <t>community nonprofit</t>
@@ -4533,7 +4381,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>403-615-1904</t>
@@ -4549,13 +4396,11 @@
           <t>https://www.starsathletics.ca</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>25+ years; camps and development programs year-round, Gr 1-6 focus up to all ages, facilities in SE/SW/NW/NE Calgary</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
           <t>private academy / development program</t>
@@ -4576,7 +4421,6 @@
           <t>https://www.starsathletics.ca</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4599,7 +4443,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>403-998-6395</t>
@@ -4610,7 +4453,6 @@
           <t>aweir20@gmail.com</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Adam Weir — contact (AYBC record)</t>
@@ -4631,7 +4473,6 @@
           <t>community club (parent/coach-run)</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4642,7 +4483,6 @@
           <t>https://www.aybc.ca/2020-club-members-1/sixers</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4665,7 +4505,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>403-998-6395</t>
@@ -4676,7 +4515,6 @@
           <t>aweir20@gmail.com</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Adam Weir — club contact (AYBC directory)</t>
@@ -4697,7 +4535,6 @@
           <t>private club</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>reported</t>
@@ -4708,7 +4545,6 @@
           <t>https://www.aybc.ca/2020-club-members-1/sixers</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4731,8 +4567,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>admin@sccba.ca</t>
@@ -4805,8 +4639,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>president@southstoneybasketball.com</t>
@@ -4879,8 +4711,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>president@southstoneybasketball.com</t>
@@ -4891,7 +4721,6 @@
           <t>https://southstoneybasketball.com/</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>House-league youth basketball; inaugural season September 2026; games every other weekend with continuous re-seeding</t>
@@ -4969,7 +4798,6 @@
           <t>https://www.supremehoopscanada.com</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>Elite club: rep teams U13/U14/U15/U18 boys &amp; girls; training; work-to-play financial assistance</t>
@@ -5027,7 +4855,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>403-239-3752</t>
@@ -5038,7 +4865,6 @@
           <t>bkadams@shaw.ca</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Brian Adams — contact (AYBC record)</t>
@@ -5059,7 +4885,6 @@
           <t>community club (parent/coach-run)</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5070,7 +4895,6 @@
           <t>https://www.aybc.ca/2020-club-members-1/the-tech-shop</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5093,7 +4917,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>403-970-0784</t>
@@ -5104,7 +4927,6 @@
           <t>titansbasketballyyc@gmail.com</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Misellie Malig — club contact (AYBC directory)</t>
@@ -5125,7 +4947,6 @@
           <t>private club</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>reported</t>
@@ -5136,7 +4957,6 @@
           <t>https://www.aybc.ca/2020-club-members-1/titans-basketball</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5159,7 +4979,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>403-834-4766</t>
@@ -5237,7 +5056,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>587-999-2510</t>
@@ -5345,13 +5163,11 @@
           <t>Basketball programs listed for Calgary among its cities</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
           <t>private academy (multi-city: Winnipeg/Calgary/Edmonton/Fraser Valley)</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -5389,7 +5205,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>(587) 718-7005</t>
@@ -5467,7 +5282,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>403-918-3940</t>
@@ -5478,7 +5292,6 @@
           <t>fugel6@telus.net</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Shelley Nadine Fugel — contact (AYBC record)</t>
@@ -5499,7 +5312,6 @@
           <t>community club (girls-only)</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5510,7 +5322,6 @@
           <t>https://www.aybc.ca/2020-club-members-1/wings-girls-basketball</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5573,7 +5384,6 @@
           <t>multi-sport org (charity)</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>verified</t>
@@ -5611,7 +5421,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>403-714-3199</t>
@@ -5622,7 +5431,6 @@
           <t>mjamias@shaw.ca</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Mark Jamias — contact (AYBC record)</t>
@@ -5643,7 +5451,6 @@
           <t>community club (parent/coach-run)</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5654,7 +5461,6 @@
           <t>https://www.aybc.ca/2020-club-members-1/yyc-wolves</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5677,7 +5483,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>403-390-9767</t>
@@ -5688,7 +5493,6 @@
           <t>kvanweber@gmail.com</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Kelly Van Weber — contact (AYBC record)</t>
@@ -5709,7 +5513,6 @@
           <t>community club (parent/coach-run)</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5720,7 +5523,6 @@
           <t>https://www.aybc.ca/2020-club-members-1/yyccrush-basketball</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5743,7 +5545,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>403-461-8981</t>
@@ -5754,7 +5555,6 @@
           <t>ladde.tanner@astrazeneca.com</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Ladde Tanner — contact (AYBC record)</t>
@@ -5775,7 +5575,6 @@
           <t>community club (parent/coach-run)</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5786,7 +5585,6 @@
           <t>https://www.aybc.ca/2020-club-members-1/youngbloods-basketball-club</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5829,19 +5627,16 @@
           <t>https://www.instagram.com/alberta.elite/</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>Competitive youth club based in east-central Alberta</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
           <t>private club</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5884,7 +5679,6 @@
           <t>Games at University of Alberta Augustana Campus Gym, 4901-46 Avenue, Camrose, AB T4V 2R3</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>info@ejballers.com</t>
@@ -5895,7 +5689,6 @@
           <t>https://ejballers.com/index.php/ballers-league-camrose/</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>Weekly 60-minute game leagues: boys &amp; girls grades 4–8 and boys grades 9–12; Sept–Nov season; $220; part of proceeds to U of A Augustana Vikings men's basketball.</t>
@@ -5983,7 +5776,6 @@
           <t>Development program ages 8-18; fall program Sept-Dec; elite/performance team season mid-March to mid-June</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
           <t>private academy / club</t>
@@ -6031,7 +5823,6 @@
           <t>Cardston</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>403-308-8507</t>
@@ -6042,7 +5833,6 @@
           <t>BJNISH@GMAIL.COM</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Jody Nish — club contact (AYBC directory)</t>
@@ -6063,7 +5853,6 @@
           <t>community club</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>primary</t>
@@ -6121,19 +5910,16 @@
           <t>https://www.facebook.com/share/18prQV7bCR/</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>Youth basketball (Cardston / Blood Reserve–Chief Mountain area)</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>primary</t>
@@ -6171,7 +5957,6 @@
           <t>Chestermere</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>403-667-0759</t>
@@ -6249,31 +6034,26 @@
           <t>Chestermere</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>(213) 986-9582</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>https://www.instagram.com/wolfpackclubbasketball/</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>Boys club basketball program based out of Chestermere focused on player, person, skills and hard work (Instagram bio)</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
           <t>private club (boys)</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>reported</t>
@@ -6311,14 +6091,11 @@
           <t>Coaldale</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>nicole.hanna@pallisersd.ab.ca</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Nicole Hanna — club contact (per AYBC listing; role unconfirmed)</t>
@@ -6339,7 +6116,6 @@
           <t>community club</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
           <t>primary</t>
@@ -6377,7 +6153,6 @@
           <t>Coalhurst</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>403-894-8698</t>
@@ -6388,7 +6163,6 @@
           <t>coalhurstminorbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Brent Larson — club contact (AYBC directory)</t>
@@ -6409,7 +6183,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
           <t>primary</t>
@@ -6447,7 +6220,6 @@
           <t>Cochrane</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>403-542-0893</t>
@@ -6458,7 +6230,6 @@
           <t>cochranechaos@gmail.com</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Alison Laidlaw — contact (AYBC record)</t>
@@ -6479,7 +6250,6 @@
           <t>community club (girls)</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>verified</t>
@@ -6517,8 +6287,6 @@
           <t>Cochrane</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>cochraneminorbasketballassoc@gmail.com</t>
@@ -6564,7 +6332,6 @@
           <t>https://www.cochraneminorbasketball.com</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6587,7 +6354,6 @@
           <t>Cochrane</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>403-354-4327</t>
@@ -6665,21 +6431,16 @@
           <t>Devon</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>https://devonbasketball.weebly.com/</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>Intro spring program (April-May) for K-Grade 6 boys &amp; girls; skills-focused, based on Canada Basketball LTAD</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
           <t>community nonprofit</t>
@@ -6700,7 +6461,6 @@
           <t>https://devonbasketball.weebly.com/</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6723,7 +6483,6 @@
           <t>Diamond Valley (Turner Valley/Black Diamond)</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>587-830-3655</t>
@@ -6734,7 +6493,6 @@
           <t>diamondvalleyclubbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>James Holladay — club contact (AYBC directory)</t>
@@ -6755,7 +6513,6 @@
           <t>private club (girls)</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
           <t>reported</t>
@@ -6808,20 +6565,16 @@
           <t>tricountybroncos@gmail.com</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>Youth basketball serving tri-county rural area (Didsbury region)</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>primary</t>
@@ -6879,19 +6632,16 @@
           <t>https://alelitehoops.ca/</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>Club teams 13U B, 15U B/G, 17U B/G; skill development, strength &amp; conditioning, exposure/showcases; coaches: Arshan Uppal, Blind Rajab, Asad Maie, Amanni Chaaban, Adam Alas</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>verified</t>
@@ -6934,7 +6684,6 @@
           <t>P.O. Box 41030, Edmonton, AB T6J 6M7</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>info@cadasports.com</t>
@@ -6980,7 +6729,6 @@
           <t>https://www.cadasports.com/</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7003,8 +6751,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
           <t>craig.frizzell@hotmail.com</t>
@@ -7082,8 +6828,6 @@
           <t>6034 83 St NW, Edmonton, AB</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>https://www.climbbasketball.ca/home</t>
@@ -7109,7 +6853,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
           <t>verified</t>
@@ -7187,7 +6930,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
           <t>verified</t>
@@ -7245,7 +6987,6 @@
           <t>https://edmontonproambasketball.com/</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>Summer youth league (July-Aug) U11-U18 boys &amp; girls competitive + rec divisions; spring league teams U13/U15/U18 boys; 1-on-1/small-group training (NCCP certified), all-girls program, camps, Kings Court tournament; travel to Edmonton/Calgary/Vancouver events</t>
@@ -7303,13 +7044,11 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>(780) 257-3438</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>https://edmsouthsidehoops.ca/</t>
@@ -7350,7 +7089,6 @@
           <t>https://edmsouthsidehoops.ca/</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7373,7 +7111,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>587-938-7264</t>
@@ -7389,19 +7126,16 @@
           <t>https://eliteacesathletics.com/basketball</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>Competitive teams 11U through 17U/HS boys &amp; girls; training camps; hosts Showdown Series tournament</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
           <t>primary</t>
@@ -7412,7 +7146,6 @@
           <t>https://eliteacesathletics.com/basketball</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7435,8 +7168,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>info@fcvhoops.ca</t>
@@ -7447,7 +7178,6 @@
           <t>https://www.fcvhoops.ca/</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>Competitive youth teams in south/SW Edmonton ages 10-15; spring teams with weekly practices; 1-on-1 and small-group training, camps</t>
@@ -7463,7 +7193,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
           <t>verified</t>
@@ -7474,7 +7203,6 @@
           <t>https://www.fcvhoops.ca/</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7537,7 +7265,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
           <t>verified</t>
@@ -7580,7 +7307,6 @@
           <t>Legacy Athletics, 9748 12 Ave SW, Edmonton, AB</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
           <t>admin@genesisbasketballyeg.ca</t>
@@ -7653,7 +7379,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>780-238-0814</t>
@@ -7669,13 +7394,11 @@
           <t>https://www.hpadbasketball.com/</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>Travel AAU-style club for Edmonton, Nisku, Leduc &amp; Sherwood Park athletes ~14-17; club teams, winter academy, MADE Hoops competitive circuit participation</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
           <t>private academy</t>
@@ -7743,7 +7466,6 @@
           <t>https://www.hoopdreamsbasketball.ca/</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>Youth development for all ages/levels with skill tracking; 1-on-1 private training; greater Edmonton area</t>
@@ -7806,26 +7528,21 @@
           <t>Saville Community Sports Centre, University of Alberta South Campus, Edmonton, AB</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>https://bearsandpandas.ca/sports/2020/10/21/junior-bears-basketball-club.aspx</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>Spring club program (April to early July) run as extension of the Golden Bears varsity program; skill development, advanced team concepts, strength &amp; conditioning at Sports Performance Centre</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
           <t>multi-sport org (university varsity-extension program)</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
           <t>primary</t>
@@ -7868,20 +7585,16 @@
           <t>MacEwan University, Edmonton, AB</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
           <t>https://www.macewangriffins.ca/camps/jrgriffins</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>Summer youth basketball camps (also volleyball/hockey) run by Griffins varsity athletes/coaches; all abilities, boys &amp; girls, grouped by age/skill; Mon-Fri 9am-4pm; aligned to Canada Basketball LTAD</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
           <t>multi-sport org (university camp program)</t>
@@ -7934,7 +7647,6 @@
           <t>9748 12 Ave SW, Edmonton, AB</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
           <t>info@legacyathletics.ca</t>
@@ -7945,7 +7657,6 @@
           <t>https://www.legacyathletics.ca/</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>Six-court private facility; Little/Jr. Legacies ages 2-8; EYBA Development Program ages 9-17; ELITE+ training; ITD Panthers club teams U11 girls &amp; boys, U12-U17 boys, U13/U15/U17 girls (5 tournaments/yr, optional July travel team); summer camps; adult Legacy League; 3x3 summer league; hosts Canada Basketball Academy (Alberta Basketball) Sundays</t>
@@ -8023,13 +7734,11 @@
           <t>https://www.nwebc.ca/</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>Est. Feb 2016, ~500 members; Elite Knights teams U11/U13/U15 boys, U13/U15 girls; fall &amp; winter training</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>private academy</t>
@@ -8082,7 +7791,6 @@
           <t>Box 31135 Namao Centre, Edmonton, AB T5Z 3P3</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>info@northeastbasketball.com</t>
@@ -8155,7 +7863,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>780-908-8059</t>
@@ -8171,13 +7878,11 @@
           <t>https://www.nwebc.ca/</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>Training camps for girls and boys ages 7-16; fall (Sep-Dec), winter (Jan-Mar) and spring (Apr-Jun) sessions; 150+ kids registered, ~500 members with waiting list; established Feb 2016</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
           <t>community club (nonprofit status not published)</t>
@@ -8225,11 +7930,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>Competitive club teams (age groups per EYBA/ABA team pages); tournament travel (e.g. Rocky Mountain Challenge)</t>
@@ -8245,7 +7945,6 @@
           <t>club (type unpublished)</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
           <t>reported</t>
@@ -8283,11 +7982,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>Community basketball program for Edmonton youth ages 8-17; skill development and mentorship focus</t>
@@ -8303,7 +7997,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
           <t>primary</t>
@@ -8314,7 +8007,6 @@
           <t>https://www.abbasketball.ca/content/northside-hoops</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8342,7 +8034,6 @@
           <t>PO Box 57053, Edmonton, AB T5T 4J5</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
           <t>info@northwestbasketball.ca</t>
@@ -8415,7 +8106,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>(587) 986-4008</t>
@@ -8451,7 +8141,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
           <t>primary</t>
@@ -8489,11 +8178,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>Club teams in EYBA: 13U boys, 15U girls (two teams), 18U boys</t>
@@ -8509,7 +8193,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -8547,11 +8230,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>Club teams in 13U boys/girls, 15U girls, 18U boys per EYBA team pages</t>
@@ -8567,7 +8245,6 @@
           <t>club (type unpublished)</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -8692,7 +8369,6 @@
           <t>P.O. Box 21018 RPO Terwillegar, Edmonton, AB T6R 2V4</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
           <t>info@southwestbasketball.com</t>
@@ -8867,7 +8543,6 @@
           <t>https://www.truenorthbasketballacademy.com/</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>Team + training program fall/winter/spring for U11/U13/U15/U18 (tryout-selected); Saturday skills, summer camps, shooting/individual training, elite/prep academy; ages 6-18</t>
@@ -8925,8 +8600,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
           <t>westelitebasketball@gmail.com</t>
@@ -9004,7 +8677,6 @@
           <t>3804 139 Avenue, Edmonton, AB</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
           <t>wolves@freeplayforkids.com</t>
@@ -9025,7 +8697,6 @@
           <t>Accessible/inclusive multi-sport club (basketball, soccer, ball hockey, ice hockey); Jr. Wolves basketball ages 10-13; 'Contribute What You Can' membership; Canada Basketball Verified</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
           <t>multi-sport org</t>
@@ -9093,13 +8764,11 @@
           <t>https://youthhoops.ca/</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>10-week training programs ages 7-16 all levels; Summer Burst camp; Elite Core program; partners with Shoot 360 Sherwood Park and Edmonton Stingers</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
           <t>private academy</t>
@@ -9120,7 +8789,6 @@
           <t>https://youthhoops.ca/</t>
         </is>
       </c>
-      <c r="P122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -9143,8 +8811,6 @@
           <t>Edson</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
           <t>edsonminorbasketball@gmail.com</t>
@@ -9155,7 +8821,6 @@
           <t>http://www.edsonminorbasketball.com/</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>Minor basketball with ABA annual membership; 'Edson Raiders' club teams; separate Edson Mini Basketball SNYB program (contact Mike Andrews, 780-723-6035, edsonminibasketball@hotmail.ca)</t>
@@ -9213,23 +8878,16 @@
           <t>Edson</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>edsonminorbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
           <t>competitive club</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
           <t>reported</t>
@@ -9267,15 +8925,11 @@
           <t>Fort McMurray</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>https://www.facebook.com/fmelitebasketball/</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>Travel teams for dedicated players; high-level training; competitive games vs clubs around the province</t>
@@ -9291,7 +8945,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
         <is>
           <t>reported</t>
@@ -9339,25 +8992,21 @@
           <t>(780) 370-5437</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
           <t>https://www.facebook.com/MakinHoopsClub/</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>Child-centered basketball programs.</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
           <t>private club/program</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
           <t>reported</t>
@@ -9395,13 +9044,11 @@
           <t>Fort McMurray</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>780-881-2968</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
           <t>https://northerntrailblazers.com/</t>
@@ -9474,22 +9121,16 @@
           <t>9908 Penhorwood St, Fort McMurray, AB T9H 1L3</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>https://www.facebook.com/profile.php?id=61579214611190</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
           <t>reported</t>
@@ -9527,7 +9168,6 @@
           <t>Fort Saskatchewan</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>403-307-6257</t>
@@ -9543,13 +9183,11 @@
           <t>https://www.fsybasketball.com/</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>Grassroots program ages 5-12; 11U &amp; 13U house leagues, season September-December; coach RCMP vulnerable-sector checks and Alberta Basketball/Basketball Canada memberships included</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
           <t>community nonprofit (division of Fort Saskatchewan Minor Sports Association, multi-sport org)</t>
@@ -9597,8 +9235,6 @@
           <t>Grande Prairie</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
           <t>auroranorthbasketball@gmail.com</t>
@@ -9609,19 +9245,16 @@
           <t>https://www.facebook.com/profile.php?id=61551046507977</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>Youth basketball academy</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr">
         <is>
           <t>reported</t>
@@ -9664,7 +9297,6 @@
           <t>11850 108 St, Grande Prairie, AB T8V 8G5</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
           <t>gpelite23@outlook.com</t>
@@ -9685,7 +9317,6 @@
           <t>Competitive youth club basketball; year-round registration</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
           <t>private club</t>
@@ -9753,7 +9384,6 @@
           <t>https://grandeprairiegilasbasketball.com/</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>Multicultural nonprofit for ages 10–18, male and female; spring travel teams (tryouts Feb–Mar); works with JumpStart/KidSport for fee assistance; Alberta Basketball membership.</t>
@@ -9811,7 +9441,6 @@
           <t>Grande Prairie</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>780-512-6699</t>
@@ -9837,13 +9466,11 @@
           <t>1-on-1 training, group camps (fundamentals, conditioning, team dynamics) for GP youth</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr">
         <is>
           <t>primary</t>
@@ -9881,7 +9508,6 @@
           <t>Grande Prairie</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>250-571-2766</t>
@@ -9964,7 +9590,6 @@
           <t>9919 113 Ave, Grande Prairie, AB</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
           <t>info@undergroundbasketball.ca</t>
@@ -9975,13 +9600,11 @@
           <t>https://www.undergroundbasketball.ca/</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>High-discipline youth academy with strength &amp; conditioning; programs in Grande Prairie and Whitecourt (grade 7/8 program via Town of Whitecourt rec); ABA map pin in Valleyview</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
           <t>private academy</t>
@@ -10029,23 +9652,16 @@
           <t>Hanna</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>Community youth basketball; girls U15 team (Wildcats)</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr">
         <is>
           <t>reported</t>
@@ -10083,23 +9699,16 @@
           <t>Hay Lakes</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
           <t>aholba8181@gmail.com</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr">
         <is>
           <t>reported</t>
@@ -10137,7 +9746,6 @@
           <t>La Crete</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>780-841-5667</t>
@@ -10148,7 +9756,6 @@
           <t>infinitylacrete@gmail.com</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>Brenda Wiebe — club contact (AYBC directory)</t>
@@ -10169,7 +9776,6 @@
           <t>community club</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
           <t>primary</t>
@@ -10212,7 +9818,6 @@
           <t>Box 5525, Leduc, AB T9E 2A1</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
           <t>communications@leduclightning.com</t>
@@ -10290,8 +9895,6 @@
           <t>University of Lethbridge</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>https://gohorns.ca/sports/2026/2/12/jr-horns-programs.aspx</t>
@@ -10364,7 +9967,6 @@
           <t>University of Lethbridge, Lethbridge, AB</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
           <t>kenny.otieno@uleth.ca</t>
@@ -10385,7 +9987,6 @@
           <t>Invitation-based U13-U15 and U17-U18 boys + girls teams (spring, Apr-Jun); clinics and U12-U16 camps led by Pronghorn athletes; also a Women's Junior Horns PEBL team</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
           <t>university-run youth club program</t>
@@ -10433,19 +10034,11 @@
           <t>Lethbridge</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -10483,25 +10076,21 @@
           <t>Lethbridge</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>403-393-4871</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
           <t>https://lethbridgecougars.ca/lcbc/</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>U9 development, U11/U13 development, U11-U17 spring tryout teams</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
           <t>community club</t>
@@ -10554,7 +10143,6 @@
           <t>Box 22028 Henderson Lake, Lethbridge, AB T1K 6X5</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
           <t>lethbridgebasketball@gmail.com</t>
@@ -10627,7 +10215,6 @@
           <t>Lethbridge</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>403-795-9185</t>
@@ -10638,7 +10225,6 @@
           <t>windycitybasketballclub@gmail.com</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>Mandy Butler — club contact (AYBC directory)</t>
@@ -10659,7 +10245,6 @@
           <t>community club (girls)</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr">
         <is>
           <t>primary</t>
@@ -10697,7 +10282,6 @@
           <t>Lloydminster</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>780-808-4025</t>
@@ -10805,7 +10389,6 @@
           <t>Year-round facility (1 regulation + 2 youth basketball courts, 2 volleyball courts): youth basketball camps, winter 'Hoop Factory Lloydminster Youth Basketball' program, before-school Hoop Group for HS athletes (with transport to LPSD schools), school academies; has run Lloydminster Minor Basketball sessions</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
           <t>private academy / multi-sport facility</t>
@@ -10853,21 +10436,16 @@
           <t>Lloydminster</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>https://gtshoopfactory.leagueapps.com/</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>Seasonal youth basketball programs/camps in Lloydminster (e.g. Winter 2025 session).</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
           <t>private academy program (external operator)</t>
@@ -10915,23 +10493,16 @@
           <t>Lloydminster</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>639-536-4092</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
           <t>community cultural association</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -10969,31 +10540,26 @@
           <t>Lloydminster</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>306-307-8788</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
           <t>https://www.facebook.com/p/Lloydminster-Minor-Basketball-Association-61558519229133/</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>Junior programming + league tournaments; home of the 'Maple Lloyd' teams U10-U15; 100% volunteer parent/community run</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr">
         <is>
           <t>reported</t>
@@ -11031,15 +10597,11 @@
           <t>Lloydminster</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>306-307-8788</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>Junior player programming and league/tournament play; home club of youth teams at U10–U15; 100% volunteer, parent/community-run.</t>
@@ -11055,7 +10617,6 @@
           <t>community nonprofit (volunteer-run)</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr">
         <is>
           <t>reported</t>
@@ -11093,7 +10654,6 @@
           <t>Lloydminster</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>639-840-0947</t>
@@ -11104,7 +10664,6 @@
           <t>jeffreygeraldwilson@gmail.com</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>Jeff Wilson — club contact (AYBC directory)</t>
@@ -11125,7 +10684,6 @@
           <t>community club</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
           <t>primary</t>
@@ -11163,31 +10721,26 @@
           <t>Lloydminster</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>306-307-8788</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>https://www.facebook.com/lloydyouthbasketball/</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>Youth basketball programming</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr">
         <is>
           <t>reported</t>
@@ -11230,7 +10783,6 @@
           <t>Lakeland College Lloydminster campus gym</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
           <t>director@rustlersyouthbasketball.ca</t>
@@ -11251,7 +10803,6 @@
           <t>Co-ed youth basketball in 4 age groups; goal to foster participation and enjoyment.</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
           <t>college-affiliated community program</t>
@@ -11309,9 +10860,6 @@
           <t>403-758-3366</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
           <t>Youth teams entering Alberta Basketball events (e.g. 11U boys at Youth Provincials).</t>
@@ -11327,7 +10875,6 @@
           <t>community club</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr">
         <is>
           <t>reported</t>
@@ -11365,11 +10912,6 @@
           <t>Magrath</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
           <t>Boys (Rockets) and girls (Pandas) youth teams</t>
@@ -11385,7 +10927,6 @@
           <t>community club</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr">
         <is>
           <t>reported</t>
@@ -11423,7 +10964,6 @@
           <t>Medicine Hat</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>403-977-4545</t>
@@ -11501,11 +11041,6 @@
           <t>Medicine Hat</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
           <t>Operates the Grade 5–7 developmental league in Medicine Hat (the 'Med Hat Minor Basketball League' on the mapped-league list); clubs like Rangers feed sessions into it.</t>
@@ -11521,7 +11056,6 @@
           <t>community nonprofit (league operator)</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr">
         <is>
           <t>reported</t>
@@ -11559,8 +11093,6 @@
           <t>Medicine Hat</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
           <t>medicinehatgoldenhawks@outlook.com</t>
@@ -11571,7 +11103,6 @@
           <t>https://www.goldenhawksbasketballclub.com/</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>Spring club teams with tryouts; registration promoted through Monsignor McCoy High School.</t>
@@ -11587,7 +11118,6 @@
           <t>competitive club (spring)</t>
         </is>
       </c>
-      <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr">
         <is>
           <t>primary</t>
@@ -11625,7 +11155,6 @@
           <t>Medicine Hat</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>403-952-9180</t>
@@ -11661,7 +11190,6 @@
           <t>community club organization</t>
         </is>
       </c>
-      <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr">
         <is>
           <t>verified</t>
@@ -11704,7 +11232,6 @@
           <t>PO Box 10062, Morinville RPO, Morinville, AB T8R 0A4</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
           <t>ask.myba@gmail.com</t>
@@ -11715,7 +11242,6 @@
           <t>http://www.morinvilleyouthbasketball.com/</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>Youth basketball ages 5-17 for Morinville, Sturgeon County and surrounding areas; U11 and up; board of trustees elected at AGM</t>
@@ -11773,7 +11299,6 @@
           <t>Okotoks</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>403-336-6503</t>
@@ -11824,7 +11349,6 @@
           <t>https://bigrockbball.ca</t>
         </is>
       </c>
-      <c r="P162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11847,14 +11371,11 @@
           <t>Okotoks</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>403-801-8488</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>Jason Cyr — contact (AYBC record)</t>
@@ -11875,7 +11396,6 @@
           <t>community club/academy</t>
         </is>
       </c>
-      <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr">
         <is>
           <t>primary</t>
@@ -12050,7 +11570,6 @@
           <t>https://visionbasketballacademy.com/locations</t>
         </is>
       </c>
-      <c r="P165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -12078,8 +11597,6 @@
           <t>Olds College, Olds, AB</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
           <t>https://gobroncos.ca/</t>
@@ -12095,13 +11612,11 @@
           <t>Jr. NBA camp/program giving younger students early access to basketball; Alberta Basketball also stages CB Academy (15U/17U) sessions in Olds.</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
           <t>college-run community grassroots program</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr">
         <is>
           <t>reported</t>
@@ -12154,7 +11669,6 @@
           <t>oldshoopslab@gmail.com</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>Kyle Young, Program Founder (Teacher at Holy Trinity Catholic School)</t>
@@ -12165,13 +11679,11 @@
           <t>Youth basketball training</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
           <t>private training program/academy</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr">
         <is>
           <t>primary</t>
@@ -12229,19 +11741,16 @@
           <t>https://www.instagram.com/jdl_athletics/</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
           <t>Youth basketball training; operates Peace River Steve Nash Youth Basketball (SNYB) program</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
           <t>private training program / community SNYB operator</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr">
         <is>
           <t>primary</t>
@@ -12279,7 +11788,6 @@
           <t>Peace River</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>780-617-2583</t>
@@ -12295,19 +11803,16 @@
           <t>https://www.facebook.com/profile.php?id=100068770855153</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
           <t>Youth basketball; hosted Team Alberta North U19 tryout stop</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr">
         <is>
           <t>primary</t>
@@ -12345,15 +11850,11 @@
           <t>Peace River</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
           <t>w_bball@telus.net</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
           <t>Club basketball for Peace Country youth; U15 and U17 teams; town also has a separate Jr NBA youth program (Peace River Jr NBA Youth Basketball).</t>
@@ -12411,15 +11912,11 @@
           <t>Ponoka</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
           <t>https://www.apexathletedevelopment.ca/</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
           <t>Basketball/athlete development programs, central Alberta</t>
@@ -12477,19 +11974,11 @@
           <t>Raymond</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
           <t>community program</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -12537,8 +12026,6 @@
           <t>403-752-3381</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>Brock Dewsbery (Head Coach)</t>
@@ -12559,7 +12046,6 @@
           <t>community club</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -12597,7 +12083,6 @@
           <t>Red Deer</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>403-307-7573</t>
@@ -12608,7 +12093,6 @@
           <t>officialascendbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>Nathaniel McIntosh — club contact (AYBC directory)</t>
@@ -12629,7 +12113,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr">
         <is>
           <t>primary</t>
@@ -12667,7 +12150,6 @@
           <t>Red Deer</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>403-506-6174</t>
@@ -12683,7 +12165,6 @@
           <t>https://cabcsky.com/</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>Kings (boys) and Queens (girls) rep teams at U13, U15, U17; Junior Queens development for post-high-school athletes; ~10 teams. Founded by Red Deer Polytechnic basketball coaches; NCCP-certified coaches.</t>
@@ -12699,7 +12180,6 @@
           <t>competitive club (rep)</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr">
         <is>
           <t>primary</t>
@@ -12767,7 +12247,6 @@
           <t>Rep/club: U15 (HS prep), U17, U18 (collegiate prep); 10 teams; spring season late Mar–mid Jun ($875, 4 tournaments + exhibitions); Winter Break Elite Camp with Grow Your Game</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
           <t>community club (competitive/rep)</t>
@@ -12835,7 +12314,6 @@
           <t>https://dteliteball.teamsnapsites.com</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
           <t>Youth club/rep basketball (details on TeamSnap site)</t>
@@ -12898,7 +12376,6 @@
           <t>5121 48 Ave, Red Deer, AB T4N 6X3</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
           <t>reid@hypehoops.ca</t>
@@ -12976,7 +12453,6 @@
           <t>PO Box 26031 STN CTR, Red Deer, AB T4N 6X7</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
           <t>info@reddeerbball.ca</t>
@@ -13069,7 +12545,6 @@
           <t>https://www.splashcanadabasketball.com/</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
           <t>Elite boys teams: U13, U15, and High School divisions.</t>
@@ -13132,7 +12607,6 @@
           <t>Programs held at Notre Dame High School, Red Deer</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
           <t>perimeter.basketball.academy@gmail.com</t>
@@ -13153,7 +12627,6 @@
           <t>Skills camps for grades 5–12: Christmas boot camp, middle/high-school tryout prep camp, spring skill development.</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
           <t>private academy (camps/skills)</t>
@@ -13201,19 +12674,11 @@
           <t>Red Deer area (Highway 11 corridor)</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
           <t>competitive club</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -13251,8 +12716,6 @@
           <t>Rocky Mountain House</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
           <t>rapidsbball@gmail.com</t>
@@ -13263,7 +12726,6 @@
           <t>https://www.rockyrapidsbball.com/</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
           <t>Spring club teams (April team selections); players pay ABA membership ($20 insurance) plus club fee. Motto: 'Between the Hardwood and the Rockies: Where Legends Rise!'</t>
@@ -13341,19 +12803,16 @@
           <t>https://encountersports.ca/</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>Faith-based multi-sport org: Junior Lions co-ed spring basketball (K-Gr 5), ES Lions spring basketball tryout teams, summer basketball/volleyball/golf/hockey camps</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
           <t>multi-sport org</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr">
         <is>
           <t>verified</t>
@@ -13396,26 +12855,21 @@
           <t>Bethel Lutheran Church, Sherwood Park, AB (camp venue)</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
           <t>https://www.levelupcamps.ca/</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>'Skill Developer' basketball day camps for ages 8-13; seasonal camp schedule</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
           <t>private academy (camp provider, basketball/golf/gaming)</t>
         </is>
       </c>
-      <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr">
         <is>
           <t>primary</t>
@@ -13473,13 +12927,11 @@
           <t>https://www.shoot360.com/sherwood-park</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
           <t>Tech-enabled training franchise: academies (Little Ballers 5-6, Young Ballers 7-9, up to teens), classes, in-house 3v3 leagues, Nike camps, memberships; hosts Edmonton Stingers camps</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
           <t>private academy</t>
@@ -13547,7 +12999,6 @@
           <t>http://spotlightathleticdevelopment.com/</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
           <t>Sports performance and personal training for junior high/high school athletes; listed as a participating club on EYBA's official clubs page</t>
@@ -13563,7 +13014,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr">
         <is>
           <t>verified</t>
@@ -13683,23 +13133,16 @@
           <t>Slave Lake</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
           <t>Year-round training outside the school season; first team U16 boys (ages 13–16) began practicing mid-March.</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
           <t>community club (startup)</t>
         </is>
       </c>
-      <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr">
         <is>
           <t>reported</t>
@@ -13737,23 +13180,16 @@
           <t>Spruce Grove</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
           <t>Spring basketball club with U13 girls, U15 boys, U17 girls teams</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
           <t>club (type unpublished)</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr">
         <is>
           <t>reported</t>
@@ -13796,7 +13232,6 @@
           <t>Spruce Grove, AB</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
           <t>info@parklandbasketball.ca</t>
@@ -13807,7 +13242,6 @@
           <t>http://www.parklandbasketball.ca/</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
           <t>Co-ed recreational league (Gr 2-12, games Saturdays in Spruce Grove/Stony Plain, mid-Sept–Feb) + 'Parkland Pride' rep teams; serves Spruce Grove, Stony Plain, Parkland County</t>
@@ -13838,7 +13272,6 @@
           <t>http://www.parklandbasketball.ca/</t>
         </is>
       </c>
-      <c r="P191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -13861,8 +13294,6 @@
           <t>Spruce Grove</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
           <t>info@parklandbasketball.ca</t>
@@ -13950,20 +13381,16 @@
           <t>rhonda.lang@psd.ca</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
           <t>Rhonda Lang (Athletic Director)</t>
         </is>
       </c>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
           <t>club (type unpublished)</t>
         </is>
       </c>
-      <c r="M193" t="inlineStr"/>
       <c r="N193" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -14001,8 +13428,6 @@
           <t>St. Albert</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
           <t>admin@stalbertslam.com</t>
@@ -14075,8 +13500,6 @@
           <t>St. Albert</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
           <t>President@stalbertslam.com</t>
@@ -14122,7 +13545,6 @@
           <t>https://www.stalbertslam.com/</t>
         </is>
       </c>
-      <c r="P195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -14145,8 +13567,6 @@
           <t>St. Albert</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
           <t>info.saybl@gmail.com</t>
@@ -14219,7 +13639,6 @@
           <t>Stettler</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
           <t>403-506-1100</t>
@@ -14235,7 +13654,6 @@
           <t>https://www.facebook.com/p/Stettler-Wildcats-Club-Basketball-100090725931850/</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
           <t>Club (rep) basketball teams for Stettler youth</t>
@@ -14251,7 +13669,6 @@
           <t>community club</t>
         </is>
       </c>
-      <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr">
         <is>
           <t>primary</t>
@@ -14371,7 +13788,6 @@
           <t>Sylvan Lake</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
           <t>(403) 863-7309</t>
@@ -14387,7 +13803,6 @@
           <t>https://www.sylvanlakeclippers.ca/</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
           <t>Affordable youth basketball for grades 6-12; teams at 11U, 15U, 18U (boys); spring + fall seasons</t>
@@ -14445,19 +13860,11 @@
           <t>Taber</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr">
         <is>
           <t>reported</t>
@@ -14495,15 +13902,11 @@
           <t>Tofield</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
           <t>banderson@brsd.ab.ca</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
           <t>Youth club basketball (AYBC member club, Tofield)</t>
@@ -14519,7 +13922,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr">
         <is>
           <t>primary</t>
@@ -14562,14 +13964,11 @@
           <t>4619 50 Ave, Wetaskiwin, AB T9A 0R6</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
           <t>https://www.facebook.com/Wetaskiwin-Basketball-Club-463146107518650/</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
           <t>Community youth basketball</t>
@@ -14585,7 +13984,6 @@
           <t>community club</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr">
         <is>
           <t>primary</t>
@@ -14623,7 +14021,6 @@
           <t>Wetaskiwin</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
           <t>780-352-6018 x243</t>
@@ -14634,8 +14031,6 @@
           <t>wmba@wrps11.ca</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr"/>
-      <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>Intro program for grades 1-6 focused on skill development, cooperation, sportsmanship; 24th annual season; Wetaskiwin also listed as an EYBA member zone</t>
@@ -14651,7 +14046,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr">
         <is>
           <t>reported</t>
@@ -14694,7 +14088,6 @@
           <t>58 Sunset Blvd, Whitecourt, AB T7S 1N6</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
           <t>wctwolves.info@gmail.com</t>
@@ -14705,7 +14098,6 @@
           <t>https://rec.whitecourt.ca/whitecourt/public/booking/classes/be692a4f-e276-458f-8373-578de50a9cda</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
           <t>Community youth basketball league</t>
@@ -14988,7 +14380,6 @@
           <t>Calgary + surrounding</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Fall: 2025 dates Sept 20 – Nov 15 (Sundays: 12:00-1:15 practice/training + 1:25-3:00 games); ranking Sept 14</t>
@@ -15294,7 +14685,6 @@
           <t>Province-wide (2025 3x3 championship hosted at Saville Community Sports Centre, Edmonton)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Summer — 2025 registration opened Feb 24; 3X3 Championship games played Sat Jul 12, 2025</t>
@@ -15352,7 +14742,6 @@
           <t>Province-wide</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Events across the year; provincial 3x3 championship in July (with Club Championship)</t>
@@ -15410,7 +14799,6 @@
           <t>Province-wide</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Annual invitational tournament</t>
@@ -15530,7 +14918,6 @@
           <t>Red Deer / Central Alberta</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Fall/winter season (school-year); Spring League mid-April to mid-June ($240/player incl. t-shirt, gyms, officiating, insurance; Ravens $360)</t>
@@ -15541,7 +14928,6 @@
           <t>SportsEngine (website reddeerbball.ca + registration via reddeerbball.sportngin.com — SportNgin forms)</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>verified</t>
@@ -15584,7 +14970,6 @@
           <t>Lethbridge / southern Alberta</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Winter registration opens mid-November; SNYB &amp; Superleague run early January to end of March; club basketball late February to mid-June</t>
@@ -15642,13 +15027,11 @@
           <t>Medicine Hat</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>November to March</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>403-952-9180</t>
@@ -15696,7 +15079,6 @@
           <t>Fort McMurray / Regional Municipality of Wood Buffalo</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Fall 2026: late September – mid November (16 sessions over 8 weeks: 1 practice + 1 game per week); additional seasonal sessions</t>
@@ -15707,7 +15089,6 @@
           <t>RAMP Registrations</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>primary</t>
@@ -15750,7 +15131,6 @@
           <t>St. Albert (Edmonton metro)</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>October–March (2026/27: registration Jun 15–Aug 23; coach clinic mid-Sept; season opener early Oct; jamboree early Mar 2027)</t>
@@ -15761,7 +15141,6 @@
           <t>SportsEngine (saybl.ca / saybl.sportngin.com — 'powered by SportsEngine SRM')</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>primary</t>
@@ -15876,8 +15255,6 @@
           <t>Winter prep season (fall-spring) with travel sessions; Jan 2026 Western Canada session hosted in Calgary</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>verified</t>
@@ -21979,7 +21356,6 @@
           <t>Acme / Linden</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>rustlers.girls.basketball@gmail.com</t>
@@ -21990,7 +21366,6 @@
           <t>Chris King, Executive Director</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22003,7 +21378,6 @@
           <t>Airdrie</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>info@airdriebasketball.ca</t>
@@ -22068,13 +21442,11 @@
           <t>403-999-8074</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Jamie Newman, Director of Basketball Operations</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22102,7 +21474,6 @@
           <t>Brett Gitzel — club contact (AYBC directory)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22211,7 +21582,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>president@bowriverbasketball.com</t>
@@ -22239,7 +21609,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>info@brodierec.com</t>
@@ -22282,7 +21651,6 @@
           <t>Ryan Scruggs — contact (AYBC record)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -22295,7 +21663,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>info@ctawest.com</t>
@@ -22387,7 +21754,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>info@calgarybasketball.ca</t>
@@ -22415,13 +21781,11 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>calgarychinooksbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>https://www.calgarychinooksbasketball.com</t>
@@ -22439,7 +21803,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>grizzlies@calgarygrizzlies.ab.ca</t>
@@ -22509,7 +21872,6 @@
           <t>league@cmba.ab.ca</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>https://www.cmba.ab.ca/</t>
@@ -22527,7 +21889,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>calgarynwbasketball@gmail.com</t>
@@ -22597,7 +21958,6 @@
           <t>csbaattendance@gmail.com</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>https://csbasketball.academy</t>
@@ -22615,13 +21975,11 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>registrar@thunderbasketball.ca</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>http://thunderbasketball.ca/</t>
@@ -22671,7 +22029,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>Calwest.president@gmail.com</t>
@@ -22714,7 +22071,6 @@
           <t>Kara Vanhooren — contact (AYBC record)</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -22742,7 +22098,6 @@
           <t>Dixon Dunkle — contact (AYBC record)</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -22755,7 +22110,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>nardinecain@hotmail.com</t>
@@ -22793,7 +22147,6 @@
           <t>eatviewbb@hotmail.com</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>http://eastviewbb.ca/</t>
@@ -22875,8 +22228,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>Andy De Guzman — head trainer &amp; program director (per CochraneNow news)</t>
@@ -22995,13 +22346,11 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>admin@iconsbasketball.ca</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>https://iconsbasketball.ca/</t>
@@ -23029,8 +22378,6 @@
           <t>jejensen@gmail.com</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -23058,7 +22405,6 @@
           <t>Lee Loewen — contact (AYBC record)</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -23071,13 +22417,11 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>darryl.movefree@gmail.com</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>https://www.facebook.com/legendsbasketball.yyc/</t>
@@ -23142,7 +22486,6 @@
           <t>Dipa Hasan — contact (AYBC record)</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -23170,7 +22513,6 @@
           <t>Dipa Hasan — club contact (AYBC directory)</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -23230,7 +22572,6 @@
           <t>Pushkar Rao — contact (AYBC record)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -23258,7 +22599,6 @@
           <t>Jeff Piccirillo — contact (AYBC record)</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -23318,7 +22658,6 @@
           <t>Ray Raymond — contact (AYBC record)</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -23341,7 +22680,6 @@
           <t>Team@prolificsportsacademy.com</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>https://prolificsportsacademy.com/</t>
@@ -23423,13 +22761,11 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>respectbball@gmail.com</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>https://www.respectbasketball.ca</t>
@@ -23457,7 +22793,6 @@
           <t>info@starsathletics.ca</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>https://www.starsathletics.ca</t>
@@ -23490,7 +22825,6 @@
           <t>Adam Weir — contact (AYBC record)</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -23518,7 +22852,6 @@
           <t>Adam Weir — club contact (AYBC directory)</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -23531,7 +22864,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>admin@sccba.ca</t>
@@ -23559,7 +22891,6 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>president@southstoneybasketball.com</t>
@@ -23587,13 +22918,11 @@
           <t>Calgary</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>president@southstoneybasketball.com</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>https://southstoneybasketball.com/</t>
@@ -23621,7 +22950,6 @@
           <t>info@supremehoopscanada.com</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>https://www.supremehoopscanada.com</t>
@@ -23654,7 +22982,6 @@
           <t>Brian Adams — contact (AYBC record)</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -23682,7 +23009,6 @@
           <t>Misellie Malig — club contact (AYBC directory)</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -23838,7 +23164,6 @@
           <t>Shelley Nadine Fugel — contact (AYBC record)</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -23898,7 +23223,6 @@
           <t>Mark Jamias — contact (AYBC record)</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -23926,7 +23250,6 @@
           <t>Kelly Van Weber — contact (AYBC record)</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -23954,7 +23277,6 @@
           <t>Ladde Tanner — contact (AYBC record)</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -23977,7 +23299,6 @@
           <t>rcowan04@gmail.com</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>https://www.instagram.com/alberta.elite/</t>
@@ -23995,13 +23316,11 @@
           <t>Camrose</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>info@ejballers.com</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>https://ejballers.com/index.php/ballers-league-camrose/</t>
@@ -24066,7 +23385,6 @@
           <t>Jody Nish — club contact (AYBC directory)</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -24089,7 +23407,6 @@
           <t>chiefmountainwildcats@gmail.com</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>https://www.facebook.com/share/18prQV7bCR/</t>
@@ -24144,8 +23461,6 @@
           <t>(213) 986-9582</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>https://www.instagram.com/wolfpackclubbasketball/</t>
@@ -24163,7 +23478,6 @@
           <t>Coaldale</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>nicole.hanna@pallisersd.ab.ca</t>
@@ -24174,7 +23488,6 @@
           <t>Nicole Hanna — club contact (per AYBC listing; role unconfirmed)</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -24202,7 +23515,6 @@
           <t>Brent Larson — club contact (AYBC directory)</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -24230,7 +23542,6 @@
           <t>Alison Laidlaw — contact (AYBC record)</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -24243,7 +23554,6 @@
           <t>Cochrane</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>cochraneminorbasketballassoc@gmail.com</t>
@@ -24318,7 +23628,6 @@
           <t>James Holladay — club contact (AYBC directory)</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -24341,8 +23650,6 @@
           <t>tricountybroncos@gmail.com</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -24365,7 +23672,6 @@
           <t>al.elitehoops@gmail.com</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>https://alelitehoops.ca/</t>
@@ -24383,7 +23689,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>info@cadasports.com</t>
@@ -24411,7 +23716,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>craig.frizzell@hotmail.com</t>
@@ -24439,8 +23743,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>"Coach Slav" (lead coach; full name not published)</t>
@@ -24505,7 +23807,6 @@
           <t>proambasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>https://edmontonproambasketball.com/</t>
@@ -24528,7 +23829,6 @@
           <t>(780) 257-3438</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>"Coach G" (lead coach; full name not published)</t>
@@ -24561,7 +23861,6 @@
           <t>info@eliteacesathletics.com</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>https://eliteacesathletics.com/basketball</t>
@@ -24579,13 +23878,11 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>info@fcvhoops.ca</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>https://www.fcvhoops.ca/</t>
@@ -24635,7 +23932,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>admin@genesisbasketballyeg.ca</t>
@@ -24673,7 +23969,6 @@
           <t>hpadbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>https://www.hpadbasketball.com/</t>
@@ -24701,7 +23996,6 @@
           <t>info@hoopdreamsbasketball.ca</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>https://www.hoopdreamsbasketball.ca/</t>
@@ -24719,13 +24013,11 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>info@legacyathletics.ca</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>https://www.legacyathletics.ca/</t>
@@ -24753,7 +24045,6 @@
           <t>info@nwebc.ca</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>https://www.nwebc.ca/</t>
@@ -24771,7 +24062,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>info@northeastbasketball.com</t>
@@ -24809,7 +24099,6 @@
           <t>info@nwebc.ca</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>https://www.nwebc.ca/</t>
@@ -24827,7 +24116,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
           <t>info@northwestbasketball.ca</t>
@@ -24919,7 +24207,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
           <t>info@southwestbasketball.com</t>
@@ -24989,7 +24276,6 @@
           <t>office@truenorthbasketballacademy.com</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>https://www.truenorthbasketballacademy.com/</t>
@@ -25007,7 +24293,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>westelitebasketball@gmail.com</t>
@@ -25035,7 +24320,6 @@
           <t>Edmonton</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
           <t>wolves@freeplayforkids.com</t>
@@ -25073,7 +24357,6 @@
           <t>youthhoopsinc@gmail.com</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>https://youthhoops.ca/</t>
@@ -25091,13 +24374,11 @@
           <t>Edson</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
           <t>edsonminorbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>http://www.edsonminorbasketball.com/</t>
@@ -25115,14 +24396,11 @@
           <t>Edson</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
           <t>edsonminorbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -25140,8 +24418,6 @@
           <t>(780) 370-5437</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>https://www.facebook.com/MakinHoopsClub/</t>
@@ -25164,7 +24440,6 @@
           <t>780-881-2968</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>Rachel Ivey — Director of Junior Programs &amp; House League (other leadership: Adri Ivey, Layal Abbas, Jason Ferguson, Grace Lokole; president not published)</t>
@@ -25197,7 +24472,6 @@
           <t>fortsaskyouthbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>https://www.fsybasketball.com/</t>
@@ -25215,13 +24489,11 @@
           <t>Grande Prairie</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
           <t>auroranorthbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>https://www.facebook.com/profile.php?id=61551046507977</t>
@@ -25239,7 +24511,6 @@
           <t>Grande Prairie</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
           <t>gpelite23@outlook.com</t>
@@ -25277,7 +24548,6 @@
           <t>gpgilasbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>https://grandeprairiegilasbasketball.com/</t>
@@ -25359,13 +24629,11 @@
           <t>Grande Prairie</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
           <t>info@undergroundbasketball.ca</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>https://www.undergroundbasketball.ca/</t>
@@ -25383,14 +24651,11 @@
           <t>Hay Lakes</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>aholba8181@gmail.com</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -25418,7 +24683,6 @@
           <t>Brenda Wiebe — club contact (AYBC directory)</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -25431,7 +24695,6 @@
           <t>Leduc</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>communications@leduclightning.com</t>
@@ -25459,8 +24722,6 @@
           <t>Lethbridge</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>Run by Pronghorns coaching staff (program of U of L Athletics)</t>
@@ -25483,7 +24744,6 @@
           <t>Lethbridge</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
           <t>kenny.otieno@uleth.ca</t>
@@ -25516,8 +24776,6 @@
           <t>403-393-4871</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>https://lethbridgecougars.ca/lcbc/</t>
@@ -25535,7 +24793,6 @@
           <t>Lethbridge</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>lethbridgebasketball@gmail.com</t>
@@ -25578,7 +24835,6 @@
           <t>Mandy Butler — club contact (AYBC directory)</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -25660,9 +24916,6 @@
           <t>639-536-4092</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -25680,8 +24933,6 @@
           <t>306-307-8788</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>https://www.facebook.com/p/Lloydminster-Minor-Basketball-Association-61558519229133/</t>
@@ -25704,9 +24955,6 @@
           <t>306-307-8788</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -25734,7 +24982,6 @@
           <t>Jeff Wilson — club contact (AYBC directory)</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -25752,8 +24999,6 @@
           <t>306-307-8788</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>https://www.facebook.com/lloydyouthbasketball/</t>
@@ -25771,7 +25016,6 @@
           <t>Lloydminster</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>director@rustlersyouthbasketball.ca</t>
@@ -25804,9 +25048,6 @@
           <t>403-758-3366</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -25851,13 +25092,11 @@
           <t>Medicine Hat</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>medicinehatgoldenhawks@outlook.com</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>https://www.goldenhawksbasketballclub.com/</t>
@@ -25907,13 +25146,11 @@
           <t>Morinville</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>ask.myba@gmail.com</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>http://www.morinvilleyouthbasketball.com/</t>
@@ -25968,13 +25205,11 @@
           <t>403-801-8488</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>Jason Cyr — contact (AYBC record)</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -26051,8 +25286,6 @@
           <t>Olds</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>Run with Olds College basketball coaches</t>
@@ -26090,7 +25323,6 @@
           <t>Kyle Young, Program Founder (Teacher at Holy Trinity Catholic School)</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -26113,7 +25345,6 @@
           <t>peaceriversnyb@gmail.com</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>https://www.instagram.com/jdl_athletics/</t>
@@ -26141,7 +25372,6 @@
           <t>wayne.basketball14@gmail.com</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>https://www.facebook.com/profile.php?id=100068770855153</t>
@@ -26159,14 +25389,11 @@
           <t>Peace River</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
           <t>w_bball@telus.net</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -26184,13 +25411,11 @@
           <t>403-752-3381</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>Brock Dewsbery (Head Coach)</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -26218,7 +25443,6 @@
           <t>Nathaniel McIntosh — club contact (AYBC directory)</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -26241,7 +25465,6 @@
           <t>centralalbertabc@gmail.com</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>https://cabcsky.com/</t>
@@ -26301,7 +25524,6 @@
           <t>info.dteliteball@gmail.com</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>https://dteliteball.teamsnapsites.com</t>
@@ -26319,7 +25541,6 @@
           <t>Red Deer</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
           <t>reid@hypehoops.ca</t>
@@ -26347,7 +25568,6 @@
           <t>Red Deer</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
           <t>info@reddeerbball.ca</t>
@@ -26385,7 +25605,6 @@
           <t>splashcanadabasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>https://www.splashcanadabasketball.com/</t>
@@ -26403,7 +25622,6 @@
           <t>Red Deer</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
           <t>perimeter.basketball.academy@gmail.com</t>
@@ -26431,13 +25649,11 @@
           <t>Rocky Mountain House</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
           <t>rapidsbball@gmail.com</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>https://www.rockyrapidsbball.com/</t>
@@ -26465,7 +25681,6 @@
           <t>info@encountersports.ca</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>https://encountersports.ca/</t>
@@ -26493,7 +25708,6 @@
           <t>info@shoot360shp.com</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>https://www.shoot360.com/sherwood-park</t>
@@ -26521,7 +25735,6 @@
           <t>info@spotlightathleticdevelopment.com</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>http://spotlightathleticdevelopment.com/</t>
@@ -26571,13 +25784,11 @@
           <t>Spruce Grove</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
           <t>info@parklandbasketball.ca</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>http://www.parklandbasketball.ca/</t>
@@ -26595,7 +25806,6 @@
           <t>Spruce Grove</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
           <t>info@parklandbasketball.ca</t>
@@ -26638,7 +25848,6 @@
           <t>Rhonda Lang (Athletic Director)</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -26651,7 +25860,6 @@
           <t>St. Albert</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
           <t>admin@stalbertslam.com</t>
@@ -26679,7 +25887,6 @@
           <t>St. Albert</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
           <t>President@stalbertslam.com</t>
@@ -26707,7 +25914,6 @@
           <t>St. Albert</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
           <t>info.saybl@gmail.com</t>
@@ -26745,7 +25951,6 @@
           <t>Wildcatsclubbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>https://www.facebook.com/p/Stettler-Wildcats-Club-Basketball-100090725931850/</t>
@@ -26805,7 +26010,6 @@
           <t>slclippers@gmail.com</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>https://www.sylvanlakeclippers.ca/</t>
@@ -26823,14 +26027,11 @@
           <t>Tofield</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
           <t>banderson@brsd.ab.ca</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -26853,8 +26054,6 @@
           <t>wmba@wrps11.ca</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -26867,13 +26066,11 @@
           <t>Whitecourt</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
           <t>wctwolves.info@gmail.com</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>https://rec.whitecourt.ca/whitecourt/public/booking/classes/be692a4f-e276-458f-8373-578de50a9cda</t>
@@ -26884,4 +26081,1991 @@
   <autoFilter ref="A1:F177"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C131"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Teams counted (directional)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Breakdown (league=teams)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bow River Basketball Association</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>89</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CMBA Fall/Winter League (Calgary Minor=89</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Southwest Basketball Association</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>66</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EYBA Fall/Winter League (Edmonton Yout=54; EYBA Spring League=12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>South Calgary Basketball Association</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>62</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CMBA Fall/Winter League (Calgary Minor=62</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Calgary West Basketball</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>61</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CMBA Fall/Winter League (Calgary Minor=61</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Northwest Zone Basketball Association</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>59</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EYBA Fall/Winter League (Edmonton Yout=48; EYBA Spring League=11</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Northwest Basketball</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>56</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CMBA Fall/Winter League (Calgary Minor=56</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Southeast Edmonton Basketball Association (Swarm)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>53</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EYBA Fall/Winter League (Edmonton Yout=44; EYBA Spring League=9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>North Calgary Basketball Club (NCBC) Thunder</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>52</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CMBA Fall/Winter League (Calgary Minor=52</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Strathcona Basketball Association</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>46</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EYBA Fall/Winter League (Edmonton Yout=41; EYBA Spring League=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>St. Albert SLAM Youth Basketball</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>42</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EYBA Fall/Winter League (Edmonton Yout=30; EYBA Spring League=12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Parkland Community Basketball League</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>41</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EYBA Fall/Winter League (Edmonton Yout=25; EYBA Spring League=16</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>North East Basketball Association</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>37</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EYBA Fall/Winter League (Edmonton Yout=30; EYBA Spring League=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cochrane Minor Basketball</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>34</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CMBA Fall/Winter League (Calgary Minor=27; CMBA Spring League (club season)=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Okotoks Basketball</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>33</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CMBA Fall/Winter League (Calgary Minor=33</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Airdrie Basketball</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>30</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CMBA Fall/Winter League (Calgary Minor=30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Okotoks Basketball Association (OBA club circuit)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>27</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=27</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>East Pro Basketball</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>26</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CMBA Fall/Winter League (Calgary Minor=26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Excel Basketball</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>25</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=25</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Calgary Luxor Stingrays (CLS Minor Basketball)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>24</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CMBA Fall/Winter League (Calgary Minor=14; CMBA Spring League (club season)=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Leduc &amp; County Basketball Association</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>24</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EYBA Fall/Winter League (Edmonton Yout=22; EYBA Spring League=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Millwoods Youth Basketball Association</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>23</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EYBA Fall/Winter League (Edmonton Yout=13; EYBA Spring League=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Beaumont Youth Basketball Association</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>20</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EYBA Fall/Winter League (Edmonton Yout=16; EYBA Spring League=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Bow River (South) Basketball Association</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>20</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NW Basketball (ambiguous: Calgary CMBA 'Northwest' zone OR NorthWest Edmonton Basketball/EYBA — site shows only the code 'NW', cannot disambiguate)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>19</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Calgary Basketball Academy (CBA)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>16</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=16</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>North Central Basketball Club (NCBC)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>15</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=15</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Respect Basketball</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>13</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=13</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Calgary West Basketball Association (Calwest)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>13</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=13</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SouthEast Edmonton Basketball (SEBA)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>12</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=12</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Lethbridge Minor Basketball Association (Express)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Lethbridge Minor Basketball Associatio=11</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Genesis Basketball</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>South Calgary Basketball Association (SoCal)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>10</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SouthWest Edmonton Basketball (SW)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>10</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>St. Albert Youth Basketball (SLAM)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>9</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=9</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Strathcona County Basketball (SBA)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>9</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=9</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>HoopStrength Basketball</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>8</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=8</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rise Basketball</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>8</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=8</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Open Basketball (academy/select program)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=8</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NorthEast Edmonton Basketball (NEBA)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>8</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=8</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>WBC (club code, full name unconfirmed)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>7</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EYBA Fall/Winter League (Edmonton Yout=6; EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>EastPro Basketball</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>7</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Parkland Pride Youth Basketball (PARK)</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>7</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DMS Ballers</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>6</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Rockets Basketball</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>6</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>FYB (Foothills Youth Basketball)</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Swoosh Basketball</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Okotoks Basketball Association (OBA)</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>5</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Beaumont Youth Basketball Association (BYBA)</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>5</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CCB Basketball</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Skills Elite Basketball</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>4</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Leduc &amp; County Basketball Association (LCBA)</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>4</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Cochrane Minor Basketball Association</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Wolves Athletic Club</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3x3 Edmonton Youth League=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ignite Basketball</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MENA Basketball</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Renegades Basketball</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Supreme Hoops</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Capital City Basketball</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Airdrie Minor Basketball Association (AMBA)</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Ballerettes Basketball</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Blizzards Basketball</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Tsuut'ina Warriors</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Wildfire Basketball</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>FCV Hoops</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ES Lions</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Royals Basketball</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>2</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>YEG BB</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>2</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Wolves Basketball</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Genesis YEG</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>2</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Magrath Basketball</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Wetaskiwin Basketball Club (WBC)</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>C.L.S. Minor Basketball (Chestermere/Langdon/Strathmore)</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>10STRONG U17 (standalone entry)</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>A-town</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Bow Valley Bears</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>CCTM</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Calgary Elite</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Calgary Flow</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Calgary NW</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Calgary Selects</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Cyclones</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Family Hoops</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Far East Basketball</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>HSB</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>NORCAL Basketball</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>NWBB</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Nxt Lvl Basketball Club</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Out West Basketball</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>PureHoops Basketball Club</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>RMC NW</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Spartans</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Spring Thunder</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Swish Basketball</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TAC Basketball</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>W.I.N Basketball</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>CMBA Spring League (club season)=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Halos</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Irish Basketball</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SBA Storm</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Adrenaline</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Cobras</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Bucket Squad</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Christensen</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Ascent Basketball</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Chuds Elite</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Ice Spice Elite</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>PMO Elite</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>CM Eclipse</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Risen Basketball</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Goon Gang</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Warriors</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SwarmG (independent of SEBA/Swarm zone entries)</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Wave Basketball Club</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Lions</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Falcons</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Edmonton Grads Basketball Club</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Northern Hoops Selects</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Weba Blue</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Goblins</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Goodhoops</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Altitude Black</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>GOOD (Atwal)</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Strathcona Stingers</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Armour</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Knights</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>FSYB</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Summit Basketball</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>EYBA Spring League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Morinville Youth Basketball Association (inferred from EYBA's associations directory naming pattern, e.g. BYBA=Beaumont)</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Raymond Basketball</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Alberta Basketball Youth Provincials (=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Ballerz</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>3x3 Edmonton Youth League=1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C131"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/research/provinces/SportsHub-Alberta.xlsx
+++ b/docs/research/provinces/SportsHub-Alberta.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Club Sizes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$Q$204</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$240</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$177</definedName>
@@ -65,11 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P204"/>
+  <dimension ref="A1:Q204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -454,6 +455,7 @@
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,6 +539,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Teams Counted</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -671,6 +678,9 @@
           <t>https://airdriebasketball.ca/executive</t>
         </is>
       </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -959,6 +969,9 @@
           <t>Phone as reported in search result for byba.ca</t>
         </is>
       </c>
+      <c r="Q7" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1242,6 +1255,9 @@
           <t>Being replaced (with SoCal) by the new South Stoney Basketball Association CMBA zone as of 2026.</t>
         </is>
       </c>
+      <c r="Q11" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1659,6 +1675,9 @@
           <t>ABA member club; Nick Tancon — Director Boys Basketball; Mark Hogan lead coach</t>
         </is>
       </c>
+      <c r="Q17" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2138,6 +2157,9 @@
           <t>Former domain calgaryselects.ca now parked/expired — club status worth confirming</t>
         </is>
       </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2617,6 +2639,9 @@
           <t>Community association (CMBA zone, NE Calgary, ages 6-17). Platform: RAMP InterActive (site + RAMP Registration Solutions). Full board on /executive: VP/Gym Coord Gary Dormer (gary.dormer@gmail.com), Treasurer Charlene Proulx (heycharlene@live.com), Secretary Liezel Erskine, Registrar Manpreet Jhinjar, Equipment Edyta Borges, Directors Eugene Danquah &amp; Sarah La Riviere — board uses personal emails, no org domain emails. ZoomInfo lists phone (403) 815-8056 and postal T3J 2R7 (unverified elsewhere, not put in phone field). Site TLS cert broken (fetched via proxy). Sources: http://eastprobasketball.ca/executive ; http://eastprobasketball.ca/ ; https://www.cmba.ab.ca/content/board-executive-and-committees ; https://www.zoominfo.com/c/east-pro-basketball/481522487</t>
         </is>
       </c>
+      <c r="Q31" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2858,6 +2883,9 @@
           <t>Site has 'Meet our President' page but name is JS-rendered and was not captured. | Also listed as: Excel Basketball Academy | enriched 2026-07-18</t>
         </is>
       </c>
+      <c r="Q34" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2992,6 +3020,9 @@
           <t>Also listed as: Far East Basketball Training League</t>
         </is>
       </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3146,6 +3177,9 @@
           <t>ABA member listing 'Genesis Basketball'; Edmonton teams appear in EYBA/YP portals as Genesis YEG | enriched 2026-07-18</t>
         </is>
       </c>
+      <c r="Q38" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3461,6 +3495,9 @@
           <t>Also listed as: MENA Basketball Foundation</t>
         </is>
       </c>
+      <c r="Q43" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3724,6 +3761,9 @@
           <t>https://www.aybc.ca/2020-club-members-1/nw-warriors</t>
         </is>
       </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3766,6 +3806,9 @@
           <t>Listed as 'No Limit Elite / Calgary' on ABA 2022-23 members list; no website found.</t>
         </is>
       </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3905,6 +3948,9 @@
           <t>Also branded 'NW Calgary Basketball Club'; Calgary Surge youth partner</t>
         </is>
       </c>
+      <c r="Q50" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3967,6 +4013,9 @@
           <t>https://www.aybc.ca/2020-club-members-1/purehoops-basketball-club</t>
         </is>
       </c>
+      <c r="Q51" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4225,6 +4274,9 @@
           <t>'Rise Up Hoops / Calgary' on ABA 2022-23 member list; multiple brand names map to one operation.</t>
         </is>
       </c>
+      <c r="Q55" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4359,6 +4411,9 @@
           <t>States member in good standing with Alberta Basketball</t>
         </is>
       </c>
+      <c r="Q57" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4833,6 +4888,9 @@
           <t>Canada Basketball verified; Jr. NBA partnership</t>
         </is>
       </c>
+      <c r="Q64" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5260,6 +5318,9 @@
           <t>ABA member club listing</t>
         </is>
       </c>
+      <c r="Q70" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6332,6 +6393,9 @@
           <t>https://www.cochraneminorbasketball.com</t>
         </is>
       </c>
+      <c r="Q86" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6657,6 +6721,9 @@
           <t>enriched 2026-07-18</t>
         </is>
       </c>
+      <c r="Q91" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6801,6 +6868,9 @@
           <t>Nonprofit, ~5 years old, development-first philosophy</t>
         </is>
       </c>
+      <c r="Q93" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7280,6 +7350,9 @@
           <t>Canada Basketball &amp; Alberta Basketball Verified Club; second phone (780) 903-7455 | enriched 2026-07-18</t>
         </is>
       </c>
+      <c r="Q100" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7357,6 +7430,9 @@
           <t>Edmonton branch of Genesis Basketball (Calgary org genesisbasketball.net); 'Genesis Basketball' on PSO member registry</t>
         </is>
       </c>
+      <c r="Q101" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7841,6 +7917,9 @@
           <t>Type: community association — NE Edmonton zone of Edmonton Youth Basketball (EYBA), ages 5-17. Full executive on http://northeastbasketball.com/executive: Donna Haggstrom (Executive Director, info@), Robin Bussiere (President &amp; Coach Liaison, CoachLiaison@northeastbasketball.com), Peter Piekema (Treasurer), Jasmine Murphy (Secretary), Rebecca VandenBorn (Registrar). PLATFORM INTEL: RAMP InterActive (website + registration + RAMP Team App). Site cert broken on HTTPS — use http.</t>
         </is>
       </c>
+      <c r="Q108" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7960,6 +8039,9 @@
           <t>Facebook-only web presence; EYBA registered club member | Also listed as: Northern Hoops Selects</t>
         </is>
       </c>
+      <c r="Q110" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8084,6 +8166,9 @@
           <t>Type: community association — formed 2012 by merger of Wellington, Aldergrove, Willowby, Parkview and Glenora community programs (NW Edmonton zone). Executive on http://northwestbasketball.ca/executive: Carr Miceli (President, info@), Brad Coleman (VP), Anne-Marie Vaasjo (Treasurer, treasurer@northwestbasketball.ca), Remko Oosterhuis (Registration Director), Rheann Kelly (Secretary/Social Media). PLATFORM INTEL: RAMP InterActive (website + registration). Site cert broken on HTTPS — use http. | Also listed as: Northwest Zone Basketball Association</t>
         </is>
       </c>
+      <c r="Q112" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8156,6 +8241,9 @@
           <t>Partners with Alberta Basketball | enriched 2026-07-18</t>
         </is>
       </c>
+      <c r="Q113" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8208,6 +8296,9 @@
           <t>EYBA clubs page links 'Rockets Basketball' to rocketsbasketball.ca which resolves to a Cole Harbour NS club — link appears stale/wrong; Edmonton club identity unverified beyond EYBA team pages</t>
         </is>
       </c>
+      <c r="Q114" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8260,6 +8351,9 @@
           <t>EYBA clubs page links this member to rocketsbasketball.ca, which is actually a Cole Harbour, Nova Scotia association — stale/wrong link; Edmonton Rockets' own web presence not found</t>
         </is>
       </c>
+      <c r="Q115" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8419,6 +8513,9 @@
           <t>One of four Edmonton quadrant zone associations under EYBA | Also listed as: Southwest Basketball Association</t>
         </is>
       </c>
+      <c r="Q117" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8501,6 +8598,9 @@
           <t>Incorporated June 2026; tournament operator at scale (400+ teams projected) — both a club and an events business | Type: private club/academy, founded January 2011 by Ron Hopkins; site notes 'Swoosh Canada Basketball Inc.' officially incorporated June 2026. Phone/email route directly to Hopkins. Custom website (not RAMP/TeamLinkt/SportsEngine). Sources: https://www.swooshcanada.com/ (address) ; https://www.swooshcanada.com/contact-us (phone/email) ; https://www.swooshcanada.com/our-story (founder)</t>
         </is>
       </c>
+      <c r="Q118" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8722,6 +8822,9 @@
           <t>enriched 2026-07-18</t>
         </is>
       </c>
+      <c r="Q121" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -9868,6 +9971,9 @@
           <t>Type: community association / rep club, non-profit; plays in EYBA. Site hosted on RAMP InterActive. Address is a PO box (no street address or phone published). Executive at https://www.leduclightning.com/executive: President Chris Burke (president@leduclightning.com), VP Kelli Warren, Secretary Randi Stassen, Treasurer Jaimie Delwisch, Registrar Kelly Valentine (registrar@leduclightning.com), EYBA Director Erin Kivitt. Sources: https://www.leduclightning.com/ ; https://www.leduclightning.com/executive</t>
         </is>
       </c>
+      <c r="Q139" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -10193,6 +10299,9 @@
           <t>Self-described as southern Alberta's only ABA-sanctioned organization; on ABA member list as 'LMBA'. Second email lethbridgeminorbasketball@gmail.com. Club-team brand 'Lethbridge Express (LMBA)' pinned separately on ABA club map.</t>
         </is>
       </c>
+      <c r="Q144" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -11277,6 +11386,9 @@
           <t>Also uses morinvilleyouthbasketball@gmail.com</t>
         </is>
       </c>
+      <c r="Q161" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11493,6 +11605,9 @@
           <t>Record 2025-26 season per Western Wheel local news (westernwheel.ca). | Also listed as: Okotoks Basketball Association (OBA)</t>
         </is>
       </c>
+      <c r="Q164" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11994,6 +12109,9 @@
           <t>Appears on Alberta Basketball association/club listing; Raymond is one of Alberta's most storied basketball towns (Raymond Comets HS dynasty) but no standalone youth-club web presence found.</t>
         </is>
       </c>
+      <c r="Q172" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -13111,6 +13229,9 @@
           <t>Street address/phone from Yelp/ZoomInfo listings; email is from official site</t>
         </is>
       </c>
+      <c r="Q188" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -13272,6 +13393,9 @@
           <t>http://www.parklandbasketball.ca/</t>
         </is>
       </c>
+      <c r="Q191" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -13344,6 +13468,9 @@
           <t>Do not confuse with parklandbasketball.com (US club) | Type: community league + rep program (Parkland Pride) serving Spruce Grove, Stony Plain, Parkland County; member of EYBA (Edmonton Youth Basketball Association). Site hosted on RAMP InterActive; registration via parklandpride.rampregistrations.com. Executives at http://www.parklandbasketball.ca/executive: President Jason Hackman (jasonh@parklandbasketball.ca), VP/Program Director Jay Ouellette (vicepresident@parklandbasketball.ca), Treasurer Jocelyn Couture, Secretary/Registrar Julie Ouellette (administration@parklandbasketball.ca), Past President Robert Bull. Secondary site/email: parklandbasketball.wordpress.com / parklandbasketball@gmail.com. Footer shows only 'Spruce Grove, AB' — no street address or phone published. Sources: http://www.parklandbasketball.ca/executive ; https://parklandbasketball.wordpress.com/about/</t>
         </is>
       </c>
+      <c r="Q192" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -13478,6 +13605,9 @@
           <t>Distinct from SAYBL (separate St. Albert house-league org) | Type: community rep/development club (since 2001). Site hosted on RAMP InterActive. Full executive board published at https://www.stalbertslam.com/executive — President Tanner Wilson (President@stalbertslam.com), VP Abdelrahman Elsabbagh (VP@stalbertslam.com), Secretary Rick Walters, Treasurer Katy Illner, Registrar Denise Barrett (Registrations@stalbertslam.com). No street address or phone published anywhere on site (contact page https://www.stalbertslam.com/content/contact-us is email-only). Socials: instagram.com/st.albertslam. Sources: https://www.stalbertslam.com/executive ; https://www.stalbertslam.com/content/contact-us</t>
         </is>
       </c>
+      <c r="Q194" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -13617,6 +13747,9 @@
           <t>Competitive-intel: one of the few Edmonton-region orgs on SportsEngine rather than RAMP | Type: community house league (boys &amp; girls ages 8-15), volunteer non-profit. Site hosted on SportsEngine (mirror: saybl.sportngin.com). Board published at https://www.saybl.ca/board: President/Treasurer Alana Gregson, VP Angela Lippolt, Secretary Jen Berglind, plus ~11 directors (registration Kayla/Ryan Groten, communications Jon/Laurie Fitzlaff, coach coordinator Sarah Dukovac). SportsEngine org directory lists board member Antony Bernadou as org contact and address only as 'St. Albert, AB T8N 0A1' (no street). saybl.ca blocks bots (403) — data pulled via direct HTML fetch. Sources: https://www.saybl.ca/board ; https://www.sportsengine.com/org/st-albert-youth-basketball-league</t>
         </is>
       </c>
+      <c r="Q196" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -13999,6 +14132,9 @@
           <t>On ABA 2022/23 good standing and official club map.</t>
         </is>
       </c>
+      <c r="Q202" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -14135,7 +14271,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P204"/>
+  <autoFilter ref="A1:Q204"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/research/provinces/SportsHub-Alberta.xlsx
+++ b/docs/research/provinces/SportsHub-Alberta.xlsx
@@ -26257,11 +26257,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CMBA Fall/Winter League (Calgary Minor=89</t>
+          <t>CMBA Fall/Winter=74 (verified 2026-07-18)</t>
         </is>
       </c>
     </row>
